--- a/data/B24_department_schedules_midterms/Gıda Mühendisliği.xlsx
+++ b/data/B24_department_schedules_midterms/Gıda Mühendisliği.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ercx2\Desktop\Scheduling Theory_02\Paper\scheduling\Campus-Scheduling\data\department_schedules_midterms\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9e402f802124af4b/Masaüstü/Projects/Campus-Scheduling/data/B24_department_schedules_midterms/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A61C1952-CABA-4CA8-A271-6D39F812CB05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="41" documentId="13_ncr:1_{A61C1952-CABA-4CA8-A271-6D39F812CB05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DA6ADF70-C87C-419C-A7C1-2A959667D65F}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20760" yWindow="-21720" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="89">
   <si>
     <t>Year:</t>
   </si>
@@ -297,13 +297,16 @@
   </si>
   <si>
     <t>CAD1,YLAB 1,YLAB 2</t>
+  </si>
+  <si>
+    <t>timeslots</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -315,6 +318,12 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -377,7 +386,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -394,11 +403,18 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="10">
+  <dxfs count="11">
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
     <dxf>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -476,16 +492,21 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{FC2381AD-6778-41F9-ACAC-AF3D65D9629E}" name="Table1" displayName="Table1" ref="A1:F35" totalsRowShown="0" headerRowDxfId="9" dataDxfId="7" headerRowBorderDxfId="8" tableBorderDxfId="6">
-  <autoFilter ref="A1:F35" xr:uid="{FC2381AD-6778-41F9-ACAC-AF3D65D9629E}"/>
-  <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{7D1FAC21-C77B-4280-8CD4-F6E89E906E16}" name="Year:" dataDxfId="5"/>
-    <tableColumn id="2" xr3:uid="{4341507C-2811-4BA6-983D-68DAB00CF0AC}" name="Course ID" dataDxfId="4"/>
-    <tableColumn id="3" xr3:uid="{7066E1F9-34A6-48B3-B554-2B2C81BCB854}" name="Date" dataDxfId="3"/>
-    <tableColumn id="4" xr3:uid="{BB1BA36B-DC26-4A18-9F1E-042D10FD23EC}" name="Rooms" dataDxfId="2"/>
-    <tableColumn id="5" xr3:uid="{4184EE83-9F6D-4BDA-9EF8-4D1266889DD2}" name="Course Name" dataDxfId="1"/>
-    <tableColumn id="6" xr3:uid="{58001B5B-8A30-41D8-8317-3016B5EA3FBB}" name="Rooms Used" dataDxfId="0"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{FC2381AD-6778-41F9-ACAC-AF3D65D9629E}" name="Table1" displayName="Table1" ref="A1:G35" totalsRowShown="0" headerRowDxfId="10" dataDxfId="8" headerRowBorderDxfId="9" tableBorderDxfId="7">
+  <autoFilter ref="A1:G35" xr:uid="{FC2381AD-6778-41F9-ACAC-AF3D65D9629E}"/>
+  <tableColumns count="7">
+    <tableColumn id="1" xr3:uid="{7D1FAC21-C77B-4280-8CD4-F6E89E906E16}" name="Year:" dataDxfId="6"/>
+    <tableColumn id="2" xr3:uid="{4341507C-2811-4BA6-983D-68DAB00CF0AC}" name="Course ID" dataDxfId="5"/>
+    <tableColumn id="3" xr3:uid="{7066E1F9-34A6-48B3-B554-2B2C81BCB854}" name="Date" dataDxfId="4"/>
+    <tableColumn id="4" xr3:uid="{BB1BA36B-DC26-4A18-9F1E-042D10FD23EC}" name="Rooms" dataDxfId="3"/>
+    <tableColumn id="5" xr3:uid="{4184EE83-9F6D-4BDA-9EF8-4D1266889DD2}" name="Course Name" dataDxfId="2"/>
+    <tableColumn id="6" xr3:uid="{58001B5B-8A30-41D8-8317-3016B5EA3FBB}" name="Rooms Used" dataDxfId="1"/>
+    <tableColumn id="7" xr3:uid="{C4BB5498-C680-4B7C-A730-E9A0396B9610}" name="timeslots" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium22" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -778,15 +799,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F35"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:I35"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="2" max="2" width="10.90625" customWidth="1"/>
-    <col min="5" max="5" width="39.90625" customWidth="1"/>
-    <col min="6" max="6" width="22.36328125" customWidth="1"/>
+    <col min="2" max="2" width="10.9296875" customWidth="1"/>
+    <col min="5" max="5" width="39.9296875" customWidth="1"/>
+    <col min="6" max="6" width="22.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -805,8 +826,11 @@
       <c r="F1" s="1" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G1" s="1" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A2" s="2">
         <v>1</v>
       </c>
@@ -825,8 +849,12 @@
       <c r="F2" s="2" t="s">
         <v>75</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G2" s="7">
+        <v>7</v>
+      </c>
+      <c r="I2" s="6"/>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A3" s="2">
         <v>1</v>
       </c>
@@ -845,8 +873,12 @@
       <c r="F3" s="2" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G3" s="7">
+        <v>5</v>
+      </c>
+      <c r="I3" s="6"/>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A4" s="2">
         <v>1</v>
       </c>
@@ -865,8 +897,12 @@
       <c r="F4" s="2" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G4" s="7">
+        <v>0</v>
+      </c>
+      <c r="I4" s="6"/>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A5" s="2">
         <v>1</v>
       </c>
@@ -885,8 +921,12 @@
       <c r="F5" s="2" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G5" s="7">
+        <v>0</v>
+      </c>
+      <c r="I5" s="6"/>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A6" s="2">
         <v>1</v>
       </c>
@@ -905,8 +945,11 @@
       <c r="F6" s="2" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G6" s="7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A7" s="2">
         <v>1</v>
       </c>
@@ -925,8 +968,12 @@
       <c r="F7" s="2" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G7" s="7">
+        <v>6</v>
+      </c>
+      <c r="I7" s="6"/>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A8" s="3">
         <v>2</v>
       </c>
@@ -945,8 +992,12 @@
       <c r="F8" s="3" t="s">
         <v>75</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G8" s="7">
+        <v>0</v>
+      </c>
+      <c r="I8" s="6"/>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A9" s="3">
         <v>2</v>
       </c>
@@ -965,8 +1016,12 @@
       <c r="F9" s="3" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G9" s="7">
+        <v>2</v>
+      </c>
+      <c r="I9" s="6"/>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A10" s="3">
         <v>2</v>
       </c>
@@ -985,8 +1040,12 @@
       <c r="F10" s="3" t="s">
         <v>75</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G10" s="7">
+        <v>2</v>
+      </c>
+      <c r="I10" s="6"/>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A11" s="3">
         <v>2</v>
       </c>
@@ -1005,8 +1064,11 @@
       <c r="F11" s="3" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G11" s="7">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A12" s="3">
         <v>2</v>
       </c>
@@ -1025,8 +1087,11 @@
       <c r="F12" s="3" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G12" s="7">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A13" s="3">
         <v>2</v>
       </c>
@@ -1045,8 +1110,11 @@
       <c r="F13" s="3" t="s">
         <v>75</v>
       </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G13" s="7">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A14" s="3">
         <v>2</v>
       </c>
@@ -1065,8 +1133,11 @@
       <c r="F14" s="3" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G14" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A15" s="3">
         <v>2</v>
       </c>
@@ -1085,8 +1156,11 @@
       <c r="F15" s="3" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G15" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A16" s="3">
         <v>2</v>
       </c>
@@ -1105,8 +1179,11 @@
       <c r="F16" s="3" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G16" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A17" s="3">
         <v>2</v>
       </c>
@@ -1125,8 +1202,11 @@
       <c r="F17" s="3" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G17" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A18" s="4">
         <v>3</v>
       </c>
@@ -1145,8 +1225,11 @@
       <c r="F18" s="4" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G18" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A19" s="4">
         <v>3</v>
       </c>
@@ -1165,8 +1248,11 @@
       <c r="F19" s="4" t="s">
         <v>75</v>
       </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G19" s="7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A20" s="4">
         <v>3</v>
       </c>
@@ -1185,8 +1271,11 @@
       <c r="F20" s="4" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G20" s="7">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A21" s="4">
         <v>3</v>
       </c>
@@ -1205,8 +1294,11 @@
       <c r="F21" s="4" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G21" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A22" s="4">
         <v>3</v>
       </c>
@@ -1225,8 +1317,11 @@
       <c r="F22" s="4" t="s">
         <v>75</v>
       </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G22" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A23" s="4">
         <v>3</v>
       </c>
@@ -1245,8 +1340,11 @@
       <c r="F23" s="4" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G23" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A24" s="4">
         <v>3</v>
       </c>
@@ -1265,8 +1363,11 @@
       <c r="F24" s="4" t="s">
         <v>86</v>
       </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G24" s="7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A25" s="4">
         <v>3</v>
       </c>
@@ -1285,8 +1386,11 @@
       <c r="F25" s="4" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G25" s="7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A26" s="5">
         <v>4</v>
       </c>
@@ -1305,8 +1409,11 @@
       <c r="F26" s="5" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G26" s="7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A27" s="5">
         <v>4</v>
       </c>
@@ -1325,8 +1432,11 @@
       <c r="F27" s="5" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G27" s="7">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A28" s="5">
         <v>4</v>
       </c>
@@ -1345,8 +1455,11 @@
       <c r="F28" s="5" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G28" s="7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A29" s="5">
         <v>4</v>
       </c>
@@ -1365,8 +1478,11 @@
       <c r="F29" s="5" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G29" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A30" s="5">
         <v>4</v>
       </c>
@@ -1385,8 +1501,11 @@
       <c r="F30" s="5" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G30" s="7">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A31" s="5">
         <v>4</v>
       </c>
@@ -1405,8 +1524,11 @@
       <c r="F31" s="5" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G31" s="7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A32" s="5">
         <v>4</v>
       </c>
@@ -1425,8 +1547,11 @@
       <c r="F32" s="5" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G32" s="7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A33" s="5">
         <v>4</v>
       </c>
@@ -1445,8 +1570,11 @@
       <c r="F33" s="5" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G33" s="7">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A34" s="5">
         <v>4</v>
       </c>
@@ -1465,8 +1593,11 @@
       <c r="F34" s="5" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G34" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A35" s="5">
         <v>4</v>
       </c>
@@ -1485,8 +1616,12 @@
       <c r="F35" s="5" t="s">
         <v>83</v>
       </c>
+      <c r="G35" s="7">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>
